--- a/plantillas/declaracion-de-aplicabilidad.xlsx
+++ b/plantillas/declaracion-de-aplicabilidad.xlsx
@@ -565,7 +565,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>5. Si agregas controles propios fuera del Anexo A, añádelos al final con el prefijo 'P-'.</t>
+          <t>5. Si agregas controles propios fuera del Anexo A, añádelos al final con el mismo identificador que usas en el registro de riesgos (por ejemplo, C-MON-02).</t>
         </is>
       </c>
     </row>
